--- a/artfynd/A 8379-2024 artfynd.xlsx
+++ b/artfynd/A 8379-2024 artfynd.xlsx
@@ -1315,7 +1315,7 @@
         <v>118325690</v>
       </c>
       <c r="B8" t="n">
-        <v>78647</v>
+        <v>78654</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>118325670</v>
       </c>
       <c r="B9" t="n">
-        <v>74528</v>
+        <v>74535</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>118325697</v>
       </c>
       <c r="B36" t="n">
-        <v>78568</v>
+        <v>78575</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
